--- a/data_extactor/batch_10_fa/batch_0005_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0005_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3DGrid HIPAA Checkup | API Healthcare ActiveStaffer | AcuStaf | Adobe Acrobat | نرم‌افزار اتوماسیون مراقبت‌های بهداشتی Allscripts | Alteer Office | American Medical Association CodeManager | Apache Hadoop | Apache Maven | Apache Pig | ArticSoft FileAssurity | Autodesk Revit | Bed Management Suite | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | CareCentric MestaMed | Cerner ProFile | Cisco Webex | نرم‌افزار رایانش ابری Citrix | CliniTrend | ColorSoft AutoMatch | ConceptDraw | نرم‌افزار مدیریت قرارداد | نرم‌افزار اصطلاحات رویه‌ای جاری CPT | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Delphi Technology | Dental Common Access System DENCAS | DxCG RiskSmart | نرم‌افزار پرونده الکترونیک سلامت EMR | Emdeon HealthPro | Epic Systems | Expert Health Data Programming Vitalnet | Facebook | FileMaker Pro | نرم‌افزار حسابداری وجوه | GE Healthcare Centricity EMR | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Ads | Google Docs | Google Drive | Google Meet | Google Sheets | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Domino | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | نرم‌افزار محیط توسعه یکپارچه IDE | Intuit QuickBooks | نرم‌افزار مدیریت مطب Kodak Dental Systems Kodak SOFTDENT PMS | LexisNexis | LinkedIn | MEDENT | MEDITECH Medical and Practice Management MPM Suite | نرم‌افزار MEDITECH | Marketo Marketing Automation | McKesson Horizon Ambulatory Care | MedFORCE Technologies WorkFLOW | نرم‌افزار کدگذاری وضعیت پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | Minitab | Misys Healthcare Systems Misys Tiger | Nuance PaperPort Professional | Oracle Business Intelligence Enterprise Edition | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Taleo | PCC EHR | PCC Pediatric Partner | Qlik Tech QlikView | R | Relative Values for Physicians | SAP Business Objects | SAP Crystal Reports | SAS | Sage 50 Accounting | نرم‌افزار Salesforce | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Tableau | TeleTracking PreAdmit-Tracking | Teradata Database | Trimble SketchUp Pro | Veritas NetBackup | نرم‌افزار مرورگر وب | نرم‌افزار Yardi | Yost Engineering ABN Assistant | Yost Engineering ClaimScrub | Yost Engineering CodeSearch Pro | Yost Engineering EPStaffCheck | Yost Engineering EpiCoder | e-MDs Bill | e-MDs Chart | e-MDs DocMan | e-MDs Schedule | نرم‌افزار eClinicalWorks EHR</t>
+          <t>3DGrid HIPAA Checkup | API Healthcare ActiveStaffer | AcuStaf | Adobe Acrobat | نرم‌افزار اتوماسیون مراقبت‌های بهداشتی Allscripts | Alteer Office | American Medical Association CodeManager | Apache Hadoop | Apache Maven | Apache Pig | ArticSoft FileAssurity | Autodesk Revit | Bed Management Suite | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | CareCentric MestaMed | Cerner ProFile | Cisco Webex | نرم‌افزار رایانش ابری Citrix | CliniTrend | ColorSoft AutoMatch | ConceptDraw | نرم‌افزار مدیریت قرارداد | نرم‌افزار اصطلاحات رویه‌ای جاری CPT | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Delphi Technology | Dental Common Access System DENCAS | DxCG RiskSmart | نرم‌افزار پرونده الکترونیک سلامت EMR | Emdeon HealthPro | Epic Systems | Expert Health Data Programming Vitalnet | Facebook | FileMaker Pro | نرم‌افزار حسابداری صندوق | GE Healthcare Centricity EMR | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Ads | Google Docs | Google Drive | Google Meet | Google Sheets | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Domino | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | نرم‌افزار محیط توسعه یکپارچه IDE | Intuit QuickBooks | Kodak Dental Systems Kodak SOFTDENT Practice management software PMS | LexisNexis | LinkedIn | MEDENT | MEDITECH Medical and Practice Management MPM Suite | نرم‌افزار MEDITECH | Marketo Marketing Automation | McKesson Horizon Ambulatory Care | MedFORCE Technologies WorkFLOW | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | Minitab | Misys Healthcare Systems Misys Tiger | Nuance PaperPort Professional | Oracle Business Intelligence Enterprise Edition | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Taleo | PCC EHR | PCC Pediatric Partner | Qlik Tech QlikView | R | Relative Values for Physicians | SAP Business Objects | SAP Crystal Reports | SAS | Sage 50 Accounting | نرم‌افزار Salesforce | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Tableau | TeleTracking PreAdmit-Tracking | Teradata Database | Trimble SketchUp Pro | Veritas NetBackup | نرم‌افزار مرورگر وب | نرم‌افزار Yardi | Yost Engineering ABN Assistant | Yost Engineering ClaimScrub | Yost Engineering CodeSearch Pro | Yost Engineering EPStaffCheck | Yost Engineering EpiCoder | e-MDs Bill | e-MDs Chart | e-MDs DocMan | e-MDs Schedule | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخنرانی | تفکر انتقادی | نوشتن | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>سخن گفتن | تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>اداره و مدیریت | زبان انگلیسی | خدمات مشتری و شخصی | پرسنل و منابع انسانی | آموزش و پرورش | رایانه و الکترونیک | اداری | پزشکی و دندانپزشکی | ریاضیات | قانون و دولت | اقتصاد و حسابداری | روانشناسی | ایمنی و امنیت عمومی</t>
+          <t>مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | پرسنل و منابع انسانی | آموزش و پرورش | رایانه و الکترونیک | اداری | پزشکی و دندان‌پزشکی | ریاضیات | قانون و دولت | اقتصاد و حسابداری | روان‌شناسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | دید نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | بحث‌های رودررو با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | نتایج کاری و خروجی‌های سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف مشابه | فراوانی تصمیم‌گیری | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های مکتوب | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | فراوانی تصمیم‌گیری | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران داده‌های بالینی | متخصصان پرستاری بالینی | هماهنگ‌کنندگان تحقیقات بالینی | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | پزشکان طب اورژانس | سرپرستان خط اول کارکنان خدمات شخصی | متخصصان آموزش سلامت | متخصصان انفورماتیک سلامت | فناوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | معلمان تخصص‌های بهداشتی، پس از متوسطه | تحلیلگران مدیریت | دستیاران پزشکی | منشی‌های پزشکی و دستیاران اداری | دستیاران کاردرمانی | نمایندگان بیمار | پزشکان طب پیشگیری | پرستاران ثبت‌نام‌شده | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه</t>
+          <t>مدیران خدمات اداری | مدیران داده‌های بالینی | متخصصان پرستاری بالینی | هماهنگ‌کنندگان تحقیقات بالینی | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | پزشکان طب اورژانس | سرپرستان خط اول کارگران خدمات شخصی | متخصصان آموزش بهداشت | متخصصان انفورماتیک سلامت | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | استادان تخصص‌های بهداشتی، پس از متوسطه | تحلیل‌گران مدیریت | دستیاران پزشکی | منشی‌های پزشکی و دستیاران اداری | کمک‌یاران کاردرمانی | نمایندگان بیمار | پزشکان طب پیشگیری | پرستاران ثبت‌شده | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>علم | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | نوشتن | سخنرانی | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>علوم | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | اداره و مدیریت | رایانه و الکترونیک | اداری | شیمی | ریاضیات | پرسنل و منابع انسانی | خدمات مشتری و شخصی</t>
+          <t>زیست‌شناسی | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | اداری | شیمی | ریاضیات | پرسنل و منابع انسانی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان شفاهی | بیان نوشتاری | درک شنیداری | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | دید نزدیک | تشخیص گفتار | اصالت | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری بستار | تسهیلات عددی | توجه انتخابی</t>
+          <t>درک کتبی | بیان شفاهی | بیان کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | اصالت | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | نتایج کاری و خروجی‌های سایر کارکنان | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | سطح رقابت | تعامل با مشتریان خارجی یا عموم مردم</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | سطح رقابت | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | مهندسان زیستی و مهندسان پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | تکنسین‌های زیستی | زیست‌شناسان | تکنسین‌های شیمی | شیمیدانان | مدیران داده‌های بالینی | هماهنگ‌کنندگان تحقیقات بالینی | دانشمندان تحقیقات رایانه و اطلاعات | دانشمندان داده | معلمان علوم زیست‌محیطی، پس از متوسطه | دانشمندان و متخصصان محیط زیست، شامل سلامت | مهندسان صنایع | تحلیلگران مدیریت | زیست‌شناسان مولکولی و سلولی | فناوران و تکنسین‌های مهندسی نانوتکنولوژی | متخصصان مدیریت پروژه | متخصصان منابع آب</t>
+          <t>مدیران معماری و مهندسی | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | تکنسین‌های زیستی | زیست‌شناسان | تکنسین‌های شیمی | شیمی‌دانان | مدیران داده‌های بالینی | هماهنگ‌کنندگان تحقیقات بالینی | دانشمندان تحقیقات کامپیوتر و اطلاعات | دانشمندان داده | مدرسان علوم محیطی، پس از متوسطه | دانشمندان و متخصصان محیط زیست، شامل بهداشت | مهندسان صنایع | تحلیل‌گران مدیریت | زیست‌شناسان مولکولی و سلولی | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | متخصصان مدیریت پروژه | متخصصان منابع آب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نوشتن | گوش دادن فعال | درک مطلب | سخنرانی | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | علم</t>
+          <t>نگارش | گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | پزشکی و دندانپزشکی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | دید نزدیک | انعطاف‌پذیری دسته‌بندی | دید دور | سرعت ادراکی | انعطاف‌پذیری بستار | تسهیلات عددی | استدلال ریاضی | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | بینایی دور | سرعت ادراکی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف مشابه | نامه‌ها و یادداشت‌های مکتوب | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | فراوانی تصمیم‌گیری</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان زیستی و مهندسان پزشکی | آمارشناسان زیستی | مدیران داده‌های بالینی | متخصصان پرستاری بالینی | دانشمندان داده | اپیدمیولوژیست‌ها | متخصصان آموزش سلامت | متخصصان انفورماتیک سلامت | فناوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | معلمان تخصص‌های بهداشتی، پس از متوسطه | دستیاران پزشکی | دانشمندان پزشکی، به جز اپیدمیولوژیست‌ها | تکنسین‌های آزمایشگاه پزشکی و بالینی | فناوران آزمایشگاه پزشکی و بالینی | مدیران خدمات پزشکی و بهداشتی | مدیران علوم طبیعی | نمایندگان بیمار | پزشکان، آسیب‌شناسان | پزشکان طب پیشگیری | دستیاران تحقیقات علوم اجتماعی</t>
+          <t>مهندسان زیستی و مهندسان زیست‌پزشکی | آمارشناسان زیستی | مدیران داده‌های بالینی | متخصصان پرستاری بالینی | دانشمندان داده | اپیدمیولوژیست‌ها | متخصصان آموزش بهداشت | متخصصان انفورماتیک سلامت | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | استادان تخصص‌های بهداشتی، پس از متوسطه | دستیاران پزشکی | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | مدیران خدمات پزشکی و بهداشتی | مدیران علوم طبیعی | نمایندگان بیمار | پزشکان، آسیب‌شناسان | پزشکان طب پیشگیری | دستیاران تحقیقات علوم اجتماعی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخنرانی | نوشتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری | علم</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | دید نزدیک | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | تسهیلات عددی | انعطاف‌پذیری بستار | روانی ایده‌ها | اصالت | استدلال ریاضی | دید دور | توجه انتخابی | سرعت ادراکی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | توانایی عددی | انعطاف‌پذیری بستار | روانی ایده‌ها | اصالت | استدلال ریاضی | بینایی دور | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | تماس با دیگران | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های مکتوب | نتایج کاری و خروجی‌های سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | فشار زمانی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | ارتباط با دیگران | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | فشار زمانی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | متخصصان بازسازی زمین‌های قهوه‌ای و مدیران سایت | مهندسان عمران | دانشمندان حفاظت | ممیزان انرژی | بازرسان انطباق زیست‌محیطی | فناوران و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل سلامت | دانشمندان و متخصصان محیط زیست، شامل سلامت | مدیران تولید زمین‌گرمایی | تکنسین‌های هیدرولوژی | هیدرولوژیست‌ها | بوم‌شناسان صنعتی | مدیران علوم طبیعی | مهندسان نفت | مدیران مراتع | مهندسان آب/فاضلاب | مدیران توسعه انرژی بادی</t>
+          <t>مهندسان کشاورزی | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مهندسان عمران | دانشمندان حفاظت | بازرسان انرژی | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | مدیران تولید زمین‌گرمایی | تکنسین‌های هیدرولوژی | آب‌شناسان | بوم‌شناسان صنعتی | مدیران علوم طبیعی | مهندسان نفت | مدیران مراتع | مهندسان آب و فاضلاب | مدیران توسعه انرژی بادی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخنرانی | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | نوشتن</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>اداره و مدیریت | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و پردازش | خدمات مشتری و شخصی | آموزش و پرورش | پرسنل و منابع انسانی | ریاضیات | اداری | رایانه و الکترونیک | حمل و نقل | قانون و دولت | روانشناسی | اقتصاد و حسابداری</t>
+          <t>مدیریت و اداره | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | خدمات مشتری و شخصی | آموزش و پرورش | پرسنل و منابع انسانی | ریاضیات | اداری | رایانه و الکترونیک | حمل و نقل | قانون و دولت | روان‌شناسی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | دید نزدیک | ترتیب‌دهی اطلاعات | بیان نوشتاری | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>تماس با دیگران | فشار زمانی | بحث‌های رودررو با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | نتایج کاری و خروجی‌های سایر کارکنان | سلامت و ایمنی سایر کارکنان | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های مکتوب | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت دقیق یا صحیح بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | موقعیت‌های تعارض | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | سخنرانی عمومی | اهمیت تکرار وظایف مشابه</t>
+          <t>ارتباط با دیگران | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | پیامدهای کاری و نتایج سایر کارکنان | سلامت و ایمنی سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | موقعیت‌های تعارض | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | سخنرانی عمومی | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | نمایندگان خدمات مشتری | دیسپچرها، به جز پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول کمک‌کاران، کارگران و جابه‌جا کنندگان مواد، دستی | سرپرستان خط اول اپراتورهای ماشین‌آلات جابه‌جایی مواد و وسایل نقلیه | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | سرپرستان خط اول کارکنان تولید و عملیات | مدیران کل و عملیات | لجستیک‌کاران | کارمندان پست و اپراتورهای ماشین‌آلات پستی، به جز خدمات پستی | تحلیلگران مدیریت | کارمندان دفتری، عمومی | کارمندان سفارش | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | مرتب‌کنندگان، پردازشگران و اپراتورهای ماشین‌آلات پردازش پست خدمات پستی | کارمندان تولید، برنامه‌ریزی و تدارکات | کارمندان حمل و نقل، دریافت و موجودی | مدیران حمل و نقل، ذخیره‌سازی و توزیع</t>
+          <t>مدیران خدمات اداری | نمایندگان خدمات مشتریان | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان رده اول کارگران تولید و بهره‌برداری | مدیران عمومی و عملیات | لجستیسین‌ها | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | تحلیل‌گران مدیریت | کارمندان دفتری عمومی | کارمندان ثبت سفارش | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارمندان ارسال، دریافت و موجودی کالا | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخنرانی | درک مطلب | گوش دادن فعال | نوشتن | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | اداره و مدیریت | اقتصاد و حسابداری | زبان انگلیسی | قانون و دولت | ایمنی و امنیت عمومی | ریاضیات | پرسنل و منابع انسانی | رایانه و الکترونیک | فروش و بازاریابی | آموزش و پرورش | اداری | ساختمان و ساخت‌وساز</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | اقتصاد و حسابداری | زبان انگلیسی | قانون و دولت | ایمنی و امنیت عمومی | ریاضیات | پرسنل و منابع انسانی | رایانه و الکترونیک | فروش و بازاریابی | آموزش و پرورش | اداری | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | تسهیلات عددی | استدلال ریاضی | دید نزدیک | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | توانایی عددی | استدلال ریاضی | بینایی نزدیک | توجه انتخابی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | نامه‌ها و یادداشت‌های مکتوب | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | نتایج کاری و خروجی‌های سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سطح رقابت | موقعیت‌های تعارض</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سطح رقابت | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | ارزیابان و ممیزان املاک و مستغلات | ارزیابان املاک شخصی و تجاری | کارمندان کارگزاری | مدیران ارشد اجرایی | مدیران ساخت‌وساز | کارمندان پیشخوان و اجاره | مدیران تأسیسات | مدیران مالی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | مدیران کل و عملیات | بازرسان و بازپرسان املاک دولتی | افسران وام | مدیران اقامتگاه | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | دلالان املاک | نمایندگان فروش املاک | مدیران فروش | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی</t>
+          <t>مدیران خدمات اداری | ارزیابان و ممیزان املاک | ارزیابان اموال شخصی و تجاری | کارمندان کارگزاری | مدیران ارشد اجرایی | مدیران ساخت‌وساز | کارمندان باجه و اجاره | مدیران تسهیلات | مدیران مالی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | مدیران عمومی و عملیات | بازرسان و محققان اموال دولتی | مسئولان وام | مدیران اقامتی | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | کارگزاران املاک | نمایندگان فروش املاک | مدیران فروش | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب | نوشتن | سخنرانی | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب | نگارش | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | اداره و مدیریت | زبان انگلیسی | روانشناسی | آموزش و پرورش | پرسنل و منابع انسانی | درمان و مشاوره | ایمنی و امنیت عمومی | اداری | جامعه‌شناسی و مردم‌شناسی | ریاضیات | رایانه و الکترونیک | قانون و دولت</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | پرسنل و منابع انسانی | درمان و مشاوره | ایمنی و امنیت عمومی | اداری | جامعه‌شناسی و انسان‌شناسی | ریاضیات | رایانه و الکترونیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | درک نوشتاری | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | بیان نوشتاری | استدلال قیاسی | اصالت | استدلال استقرایی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | دید نزدیک | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | بیان کتبی | استدلال قیاسی | اصالت | استدلال استقرایی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | محیط داخلی، دارای کنترل محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا صحیح بودن | نتایج کاری و خروجی‌های سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های مکتوب | صرف زمان برای نشستن | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سلامت و ایمنی سایر کارکنان | موقعیت‌های تعارض</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای نشستن | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سلامت و ایمنی سایر کارکنان | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | کارکنان سلامت جامعه | مدیران، فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزش، مهدکودک تا متوسطه | مدیران آموزش، پس از متوسطه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | سرپرستان خط اول کارکنان خدمات شخصی | متخصصان آموزش سلامت | مددکاران اجتماعی مراقبت‌های بهداشتی | مدیران منابع انسانی | تحلیلگران مدیریت | مدیران خدمات پزشکی و بهداشتی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مشاوران توانبخشی | مشاوران اقامتی | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران سلامت جامعه | مدیران، فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی، مهدکودک تا دبیرستان | مدیران آموزشی، پس از متوسطه | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | سرپرستان خط اول کارگران خدمات شخصی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | مدیران منابع انسانی | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | مشاوران توانبخشی | مشاوران خوابگاه و اقامتگاه | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخنرانی | نظارت | تفکر انتقادی | نوشتن | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | ریاضیات</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | اداره و مدیریت | قانون و دولت | ارتباطات و رسانه | زبان انگلیسی | مخابرات | خدمات مشتری و شخصی | آموزش و پرورش | پرسنل و منابع انسانی | رایانه و الکترونیک | حمل و نقل | جغرافیا | اداری</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | قانون و دولت | ارتباطات و رسانه | زبان انگلیسی | مخابرات | خدمات مشتری و شخصی | آموزش و پرورش | پرسنل و منابع انسانی | رایانه و الکترونیک | حمل و نقل | جغرافیا | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | استدلال قیاسی | وضوح گفتار | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | تشخیص گفتار | اصالت | انعطاف‌پذیری دسته‌بندی | دید نزدیک | تجسم | انعطاف‌پذیری بستار | سرعت بستار | دید دور | اشتراک زمان | توجه انتخابی | سرعت ادراکی</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | تشخیص گفتار | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تجسم | انعطاف‌پذیری بستار | سرعت بستار | بینایی دور | تقسیم توجه | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های مکتوب | صرف زمان برای نشستن | نتایج کاری و خروجی‌های سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای نشستن | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>رانندگان و همراهان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | برنامه‌ریزان تداوم کسب‌وکار | مدیران انطباق | تکنسین‌های فوریت‌های پزشکی | بازرسان و بازپرسان آتش‌نشانی | مهندسان پیشگیری و حفاظت در برابر آتش | سرپرستان خط اول کارکنان آتش‌نشانی و پیشگیری | سرپرستان خط اول کارکنان امنیتی | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | مهندسان امنیت اطلاعات | مدیران پیشگیری از خسارت | تحلیلگران مدیریت | مدیران خدمات پزشکی و بهداشتی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | پیراپزشکان | مخابرات‌چی‌های ایمنی عمومی | متخصصان مدیریت امنیت | مدیران امنیتی</t>
+          <t>رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | برنامه‌ریزان تداوم کسب‌وکار | مدیران انطباق | تکنسین‌های فوریت‌های پزشکی | بازرسان و محققان آتش‌نشانی | مهندسان پیشگیری و حفاظت از آتش‌سوزی | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول کارکنان امنیتی | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | مهندسان امنیت اطلاعات | مدیران پیشگیری از زیان | تحلیل‌گران مدیریت | مدیران خدمات پزشکی و بهداشتی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | پارامدیک‌ها | اپراتورهای مخابراتی امنیت عمومی | متخصصان مدیریت امنیت | مدیران امنیتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخنرانی | نظارت | نوشتن</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | اداره و مدیریت | زبان انگلیسی | اداری | اقتصاد و حسابداری | فروش و بازاریابی | روانشناسی | پرسنل و منابع انسانی | رایانه و الکترونیک | زیست‌شناسی | آموزش و پرورش | ریاضیات | قانون و دولت | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | اداری | اقتصاد و حسابداری | فروش و بازاریابی | روان‌شناسی | پرسنل و منابع انسانی | رایانه و الکترونیک | زیست‌شناسی | آموزش و پرورش | ریاضیات | قانون و دولت | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | وضوح گفتار | دید نزدیک | حساسیت به مسئله | تشخیص گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | استدلال استقرایی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | بینایی نزدیک | حساسیت به مسئله | تشخیص گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | بحث‌های رودررو با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | آزادی در تصمیم‌گیری | مجاورت فیزیکی | فشار زمانی | محیط داخلی، دارای کنترل محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | در معرض بیماری یا عفونت | نتایج کاری و خروجی‌های سایر کارکنان | نامه‌ها و یادداشت‌های مکتوب | پیامد خطا | اهمیت تکرار وظایف مشابه | محیط بیرونی، در معرض تمام شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | سخنرانی عمومی | در معرض آلاینده‌ها</t>
+          <t>مکالمات تلفنی | ایمیل | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | پیامد خطا | اهمیت تکرار وظایف یکسان | فضای باز، در معرض تمام شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | سخنرانی عمومی | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | بازپرسان مرگ | اپراتورهای کوره جسدسوزی | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مومیایی‌کنندگان | سرپرستان خط اول کارکنان خدمات شخصی | متصدیان تشییع جنازه | مدیران کل و عملیات | دستیاران بهداشت خانگی | نمایندگان فروش بیمه | مدیران خدمات پزشکی و بهداشتی | برنامه‌ریزان جلسات، کنوانسیون‌ها و رویدادها | متصدیان کفن و دفن، مسئولان تدفین و هماهنگ‌کنندگان تشییع جنازه | نمایندگان بیمار | دستیاران مراقبت شخصی | مشاوران توانبخشی | مشاوران اقامتی | مدیران خدمات اجتماعی و جامعه</t>
+          <t>مدیران خدمات اداری | مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | بازرسان مرگ | اپراتورهای کوره سوزاندن اجساد | مدیران آموزش و مراقبت از کودکان، پیش‌دبستانی و مهدکودک | مومیایی‌کنندگان | سرپرستان خط اول کارگران خدمات شخصی | متصدیان مراسم تشییع جنازه | مدیران عمومی و عملیات | کمک‌یاران سلامت در منزل | نمایندگان فروش بیمه | مدیران خدمات پزشکی و بهداشتی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مدیران مراسم تشییع، دفن و آرایشگران متوفی | نمایندگان بیمار | کمک‌یاران مراقبت شخصی | مشاوران توانبخشی | مشاوران خوابگاه و اقامتگاه | مدیران خدمات اجتماعی و جامعه</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخنرانی | نوشتن | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | اداره و مدیریت | پرسنل و منابع انسانی | فروش و بازاریابی | زبان انگلیسی | اقتصاد و حسابداری | آموزش و پرورش | روانشناسی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | پرسنل و منابع انسانی | فروش و بازاریابی | زبان انگلیسی | اقتصاد و حسابداری | آموزش و پرورش | روان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک نوشتاری | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمان | مهارت انگشت | مهارت دستی | دید دور | حفظ کردن | روانی ایده‌ها | بیان نوشتاری</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>تماس با دیگران | تعامل با مشتریان خارجی یا عموم مردم | بحث‌های رودررو با افراد و درون تیم‌ها | مجاورت فیزیکی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل محیطی | اهمیت تکرار وظایف مشابه | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دستان خود برای دست زدن، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نتایج کاری و خروجی‌های سایر کارکنان | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>هماهنگ‌کنندگان تناسب اندام و سلامتی | مدیران اسپا | مدیران خانه‌های تشییع جنازه | مدیران اقامتگاه | مدیران خدمات غذایی | مدیران قمار | مدیران سرگرمی و تفریحی، به جز قمار | مدیران کل و عملیات | مدیران خدمات اداری | مدیران املاک، مستغلات و انجمن‌های اجتماعی | مدیران خدمات اجتماعی و جامعه | مدیران منابع انسانی | مدیران فروش | مدیران بازاریابی | مدیران ارشد اجرایی | مدیران خدمات پزشکی و بهداشتی | مدیران خرید | مدیران آموزش و توسعه | سرپرستان خط اول کارکنان خدمات شخصی | کارکنان مراقبت و خدمات شخصی، سایر</t>
+          <t>هماهنگ‌کنندگان تناسب اندام و سلامتی | مدیران اسپا | مدیران خانه‌های تشییع جنازه | مدیران اقامتی | مدیران خدمات غذایی | مدیران قماربازی | مدیران سرگرمی و تفریح، به جز قماربازی | مدیران عمومی و عملیات | مدیران خدمات اداری | مدیران املاک، مستغلات و انجمن‌های اجتماعی | مدیران خدمات اجتماعی و جامعه | مدیران منابع انسانی | مدیران فروش | مدیران بازاریابی | مدیران ارشد اجرایی | مدیران خدمات پزشکی و بهداشتی | مدیران خرید | مدیران آموزش و توسعه | سرپرستان خط اول کارگران خدمات شخصی | کارکنان مراقبت شخصی و خدمات، سایر</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0005_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0005_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | نگارش | شنیدن فعال | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>سخن گفتن | تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | امور اداری و منابع انسانی | آموزش و تدریس | رایانه و الکترونیک | امور اداری و دفتری | پزشکی و دندان‌پزشکی | ریاضیات | حقوق و مقررات دولتی | اقتصاد و حسابداری | روان‌شناسی | ایمنی و امنیت عمومی</t>
+          <t>مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | پرسنل و منابع انسانی | آموزش و پرورش | رایانه و الکترونیک | اداری | پزشکی و دندان‌پزشکی | ریاضیات | قانون و دولت | اقتصاد و حسابداری | روان‌شناسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | دید نزدیک | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | اصالت و خلاقیت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران داده‌های بالینی | متخصصان پرستاری بالینی | هماهنگ‌کنندگان پژوهش‌های بالینی | مدیران مراکز پیش‌دبستانی و مهدکودک | پزشکان طب اورژانس | سرپرستان رده‌اول کارکنان خدمات فردی | کارشناسان آموزش بهداشت و ارتقای سلامت | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت آمار پزشکی | مدرسان رشته‌های تخصصی سلامت در دانشگاه | تحلیل‌گران فرایندها و سیستم‌های مدیریتی | دستیاران پزشک | منشی‌های پزشکی و مسئولان دفاتر درمانی | کمک‌یاران کاردرمانی | کارشناسان حقوق و امور بیماران | پزشکان طب پیشگیری | پرستاران دارای پروانه | مشاوران توان‌بخشی | مدیران خدمات اجتماعی و خدمات مردمی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران داده‌های بالینی | پرستاران متخصص بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | پزشکان طب اورژانس | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | کارشناسان آموزش بهداشت و ارتقای سلامت | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | کارشناسان تحلیل مدیریت و روش‌ها | کمک‌پزشکان و دستیاران مطب | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | کمک‌یاران کاردرمانی | کارشناسان امور بیماران و پذیرش | متخصصان پزشکی اجتماعی و طب پیشگیری | پرستاران | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>علوم تجربی | نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>علوم | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک | امور اداری و دفتری | شیمی | ریاضیات | امور اداری و منابع انسانی | خدمات مشتریان و خدمات فردی</t>
+          <t>زیست‌شناسی | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | اداری | شیمی | ریاضیات | پرسنل و منابع انسانی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | بیان کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | تشخیص گفتار | اصالت و خلاقیت | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری در تفکیک الگوها | مهارت در محاسبات عددی | تمرکز و توجه انتخابی</t>
+          <t>درک کتبی | بیان شفاهی | بیان کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | اصالت | روانی ایده‌ها | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | مهندسان بیوالکتریک و مهندسی پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | تکنسین‌های علوم زیستی | زیست‌شناسان | تکنسین‌های آزمایشگاه شیمی | شیمیدان‌ها | مدیران داده‌های بالینی | هماهنگ‌کنندگان پژوهش‌های بالینی | دانشمندان پژوهش‌های رایانه و اطلاعات | دانشمندان علم داده | مدرسان علوم محیط زیست در دانشگاه | دانشمندان و کارشناسان محیط زیست و بهداشت حرفه‌ای | مهندسان صنایع | تحلیل‌گران فرایندها و سیستم‌های مدیریتی | زیست‌شناسان مولکولی و سلولی | تکنسین‌ها و کارشناسان فناوری نانو | کارشناسان مدیریت پروژه | کارشناسان مدیریت منابع آب</t>
+          <t>مدیران فنی و مهندسی و معماری | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | تکنسین‌های علوم زیستی | زیست‌شناسان | تکنسین‌های شیمی | شیمی‌دانان | مدیران داده‌های بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | پژوهشگران علوم رایانه و اطلاعات | دانشمندان داده | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مهندسان صنایع | کارشناسان تحلیل مدیریت و روش‌ها | زیست‌شناسان سلولی و مولکولی | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | کارشناسان مدیریت پروژه | کارشناسان و متخصصان مدیریت منابع آب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نگارش | شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | علوم تجربی</t>
+          <t>نگارش | گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | پزشکی و دندان‌پزشکی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | دید دور | سرعت ادراک | انعطاف‌پذیری در تفکیک الگوها | مهارت در محاسبات عددی | استدلال ریاضی | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | بینایی دور | سرعت ادراکی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان بیوالکتریک و مهندسی پزشکی | متخصصان آمار زیستی | مدیران داده‌های بالینی | متخصصان پرستاری بالینی | دانشمندان علم داده | اپیدمیولوژیست‌ها | کارشناسان آموزش بهداشت و ارتقای سلامت | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت آمار پزشکی | مدرسان رشته‌های تخصصی سلامت در دانشگاه | دستیاران پزشک | دانشمندان علوم پزشکی (به‌جز اپیدمیولوژیست‌ها) | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | مدیران خدمات درمانی و بهداشتی | مدیران علوم طبیعی و پایه‌ای | کارشناسان حقوق و امور بیماران | پزشکان پاتولوژیست (آسیب‌شناس) | پزشکان طب پیشگیری | دستیاران پژوهشی علوم اجتماعی</t>
+          <t>مهندسان پزشکی و بیوانجینیرینگ | کارشناسان آمار زیستی | مدیران داده‌های بالینی | پرستاران متخصص بالینی | دانشمندان داده | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | کارشناسان آموزش بهداشت و ارتقای سلامت | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | کمک‌پزشکان و دستیاران مطب | پژوهشگران و دانشمندان علوم پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | مدیران خدمات درمانی و بهداشتی | مدیران علوم طبیعی و پایه‌ای | کارشناسان امور بیماران و پذیرش | پزشکان متخصص پاتولوژی | متخصصان پزشکی اجتماعی و طب پیشگیری | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری | علوم تجربی</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | طراحی صنعتی و فنی | فیزیک | رایانه و الکترونیک | زبان انگلیسی | جغرافیا | ساختمان و سازه | حقوق و مقررات دولتی | شیمی</t>
+          <t>مهندسی و فناوری | ریاضیات | طراحی | فیزیک | رایانه و الکترونیک | زبان انگلیسی | جغرافیا | ساختمان و ساخت‌وساز | قانون و دولت | شیمی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | تشخیص گفتار | مهارت در محاسبات عددی | انعطاف‌پذیری در تفکیک الگوها | روانی ایده‌ها | اصالت و خلاقیت | استدلال ریاضی | دید دور | تمرکز و توجه انتخابی | سرعت ادراک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | توانایی عددی | انعطاف‌پذیری بستار | روانی ایده‌ها | اصالت | استدلال ریاضی | بینایی دور | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | کارشناسان بهسازی اراضی و مدیران سایت‌های صنعتی | مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | ممیزان انرژی | بازرسان انطباق با قوانین و مقررات محیط زیست | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیا و بازسازی محیط زیست | تکنسین‌های حفاظت و علوم محیط زیست و بهداشت | دانشمندان و کارشناسان محیط زیست و بهداشت حرفه‌ای | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های هیدرولوژی و آب‌شناسی | آب‌شناسان و کارشناسان هیدرولوژی | بوم‌شناسان صنعتی | مدیران علوم طبیعی و پایه‌ای | مهندسان نفت | مدیران مراتع و آبخیزداری | مهندسان آب و فاضلاب | مدیران پروژه‌های توسعه انرژی بادی</t>
+          <t>مهندسان کشاورزی | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | ممیزان انرژی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | مدیران علوم طبیعی و پایه‌ای | مهندسان نفت | مدیران و کارشناسان مدیریت مراتع | مهندسان آب و فاضلاب | مدیران توسعه پروژه‌های انرژی بادی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فراوری | خدمات مشتریان و خدمات فردی | آموزش و تدریس | امور اداری و منابع انسانی | ریاضیات | امور اداری و دفتری | رایانه و الکترونیک | حمل‌ونقل و ترابری | حقوق و مقررات دولتی | روان‌شناسی | اقتصاد و حسابداری</t>
+          <t>مدیریت و اداره | ایمنی و امنیت عمومی | زبان انگلیسی | تولید و فرآوری | خدمات مشتری و شخصی | آموزش و پرورش | پرسنل و منابع انسانی | ریاضیات | اداری | رایانه و الکترونیک | حمل و نقل | قانون و دولت | روان‌شناسی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | دید نزدیک | مرتب‌سازی اطلاعات | بیان کتبی | انعطاف‌پذیری در طبقه‌بندی | تمرکز و توجه انتخابی | اصالت و خلاقیت | روانی ایده‌ها | انعطاف‌پذیری در تفکیک الگوها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارشناسان خدمات و پاسخگویی به مشتریان | دیسپچرها و متصدیان اعزام (به‌جز پلیس، آتش‌نشانی و اورژانس) | سرپرستان رده‌اول کارگران ساده و جابه‌جایی دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات جابه‌جایی کالا و وسایل نقلیه | سرپرستان رده‌اول کارکنان فروش غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان امور اداری و دفتری | سرپرستان رده‌اول کارکنان تولید و عملیات | مدیران ارشد اجرایی و عملیاتی | کارشناسان لجستیک و زنجیره تأمین | متصدیان نامه‌رسانی و تفکیک مرسولات دفتری | تحلیل‌گران فرایندها و سیستم‌های مدیریتی | متصدیان امور دفتری عمومی | کارمندان ثبت و پردازش سفارش‌ها | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | متصدیان و اپراتورهای ماشین‌آلات تجزیه و تفکیک پستی | کارشناسان برنامه‌ریزی، تولید و پیگیری امور اداری | کارشناسان ثبت، انبارداری و تحویل کالا | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده اول کارگران تولید و عملیات | مدیران کل و مدیران عملیات | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | کارشناسان تحلیل مدیریت و روش‌ها | متصدیان امور دفتری و امور عمومی اداری | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | اپراتورها و متصدیان تفکیک و پردازش پستی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارمندان انبار، ارسال و دریافت کالا | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | اقتصاد و حسابداری | زبان انگلیسی | حقوق و مقررات دولتی | ایمنی و امنیت عمومی | ریاضیات | امور اداری و منابع انسانی | رایانه و الکترونیک | بازاریابی و فروش | آموزش و تدریس | امور اداری و دفتری | ساختمان و سازه</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | اقتصاد و حسابداری | زبان انگلیسی | قانون و دولت | ایمنی و امنیت عمومی | ریاضیات | پرسنل و منابع انسانی | رایانه و الکترونیک | فروش و بازاریابی | آموزش و پرورش | اداری | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | مهارت در محاسبات عددی | استدلال ریاضی | دید نزدیک | تمرکز و توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | توانایی عددی | استدلال ریاضی | بینایی نزدیک | توجه انتخابی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارشناسان رسمی ارزیابی و قیمت‌گذاری املاک | ارزیابان اموال و دارایی‌های تجاری و شخصی | متصدیان امور کارگزاری و اسناد | مدیران عامل و مدیران ارشد اجرایی | مدیران پروژه‌های ساختمانی | متصدیان پذیرش، باجه و اجاره کالا | مدیران امور اماکن و تأسیسات | مدیران مالی | سرپرستان رده‌اول کارکنان امور اداری و دفتری | مدیران ارشد اجرایی و عملیاتی | بازرسان و مأموران بررسی اموال دولتی | کارشناسان اعطای تسهیلات و وام | مدیران هتل‌ها و مراکز اقامتی | کارشناسان خرید و تدارکات (به‌جز محصولات عمده‌فروشی و کشاورزی) | مدیران خرید و بازرگانی | کارگزاران و مشاوران املاک | بازاریابان و کارشناسان فروش املاک | مدیران فروش | کارشناسان فروش خدمات مالی، سهام و اوراق بهادار</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان ارزیابی اموال منقول و دارایی‌های تجاری | کارشناسان امور اداری و معاملات کارگزاری | مدیران عامل و مدیران ارشد اجرایی | مدیران پروژه‌های ساختمانی | متصدیان باجه و کرایه کالا و خدمات | مدیران امور ساختمان و تأسیسات | مدیران امور مالی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مدیران کل و مدیران عملیات | بازرسان و ممیزان اموال دولتی | کارشناسان و مسئولان تسهیلات و اعتبارات | مدیران هتل و مراکز اقامتی | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | کارگزاران و مدیران معاملات املاک | مشاوران و کارشناسان فروش املاک | مدیران فروش | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب | نگارش | سخن گفتن | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب | نگارش | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | روان‌شناسی | آموزش و تدریس | امور اداری و منابع انسانی | درمان و مشاوره‌های تخصصی | ایمنی و امنیت عمومی | امور اداری و دفتری | جامعه‌شناسی و مردم‌شناسی | ریاضیات | رایانه و الکترونیک | حقوق و مقررات دولتی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | پرسنل و منابع انسانی | درمان و مشاوره | ایمنی و امنیت عمومی | اداری | جامعه‌شناسی و انسان‌شناسی | ریاضیات | رایانه و الکترونیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | بیان کتبی | استدلال قیاسی | اصالت و خلاقیت | استدلال استقرایی | روانی ایده‌ها | مرتب‌سازی اطلاعات | دید نزدیک | انعطاف‌پذیری در تفکیک الگوها | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | بیان کتبی | استدلال قیاسی | اصالت | استدلال استقرایی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران عامل و مدیران ارشد اجرایی | مددکاران اجتماعی حوزه کودک، خانواده و مدارس | کارشناسان بهداشت و مراقبت‌های اجتماعی جامعه | مدیران امور فرهنگی، مذهبی و آموزش‌های عمومی | مدیران مقاطع تحصیلی آموزش و پرورش (ابتدایی تا متوسطه) | مدیران مراکز آموزش عالی و دانشگاهی | مدیران مراکز پیش‌دبستانی و مهدکودک | مشاوران و راهنمایان تحصیلی، شغلی و تربیتی | متصدیان بررسی صلاحیت در برنامه‌های حمایتی دولتی | سرپرستان رده‌اول کارکنان خدمات فردی | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش درمان و سلامت | مدیران منابع انسانی | تحلیل‌گران فرایندها و سیستم‌های مدیریتی | مدیران خدمات درمانی و بهداشتی | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و سوءمصرف مواد | مشاوران توان‌بخشی | سرپرستان خوابگاه‌ها و مراکز شبانه‌روزی | کمک‌یاران و دستیاران خدمات اجتماعی و مددکاری</t>
+          <t>مدیران عامل و مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | رابطان سلامت و بهورزان | مدیران فعالیت‌ها و آموزش‌های مذهبی | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | مدیران منابع انسانی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران خدمات درمانی و بهداشتی | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مشاوران توانبخشی | سرپرستان و مشاوران خوابگاه | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | تفکر انتقادی | نگارش | شنیدن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | ریاضیات</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و امور اداری | حقوق و مقررات دولتی | ارتباطات و رسانه | زبان انگلیسی | مخابرات و ارتباطات رادیویی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | امور اداری و منابع انسانی | رایانه و الکترونیک | حمل‌ونقل و ترابری | جغرافیا | امور اداری و دفتری</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | قانون و دولت | ارتباطات و رسانه | زبان انگلیسی | مخابرات | خدمات مشتری و شخصی | آموزش و پرورش | پرسنل و منابع انسانی | رایانه و الکترونیک | حمل و نقل | جغرافیا | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | روانی ایده‌ها | تشخیص گفتار | اصالت و خلاقیت | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | تجسم فضایی | انعطاف‌پذیری در تفکیک الگوها | سرعت تفکیک الگوها | دید دور | تقسیم توجه | تمرکز و توجه انتخابی | سرعت ادراک</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | تشخیص گفتار | اصالت | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تجسم | انعطاف‌پذیری بستار | سرعت بستار | بینایی دور | تقسیم توجه | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>رانندگان و متصدیان آمبولانس (به‌جز تکنسین‌های فوریت‌های پزشکی) | برنامه‌ریزان تداوم کسب‌وکار و پایداری سازمانی | مدیران انطباق با قوانین و استانداردها | تکنسین‌های فوریت‌های پزشکی | بازرسان و مأموران بررسی علل آتش‌سوزی | مهندسان ایمنی و حفاظت از حریق | سرپرستان رده‌اول اطفای حریق و امدادگران آتش‌نشانی | سرپرستان رده‌اول کارکنان حراست و نگهبانی | بازرسان و کارشناسان حفاظت از جنگل‌ها در برابر حریق | مهندسان بهداشت حرفه‌ای و ایمنی کار (به‌جز معدن) | مهندسان امنیت اطلاعات | مدیران پیشگیری از خطرات و حوادث | تحلیل‌گران فرایندها و سیستم‌های مدیریتی | مدیران خدمات درمانی و بهداشتی | کارشناسان بهداشت حرفه‌ای و ایمنی محیط کار | تکنسین‌های بهداشت حرفه‌ای و ایمنی | تکنسین‌های ارشد و کارشناسان فوریت‌های پزشکی (پارامدیک) | متصدیان بی‌سیم و مراکز پیام فوریت‌های عمومی | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات</t>
+          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | کارشناسان برنامه‌ریزی تداوم کسب‌وکار | مدیران تطبیق و نظارت مقرراتی | تکنسین‌های فوریت‌های پزشکی | بازرسان و کارشناسان بررسی علل حریق | مهندسان پیشگیری و حفاظت از حریق | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول کارکنان حراست و انتظامات | بازرسان و کارشناسان پیشگیری از حریق جنگل | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | مهندسان امنیت اطلاعات | مدیران پیشگیری از اتلاف منابع و صیانت از دارایی‌ها | کارشناسان تحلیل مدیریت و روش‌ها | مدیران خدمات درمانی و بهداشتی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | اپراتورهای فوریت‌های پلیسی و امدادی | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نظارت | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | امور اداری و دفتری | اقتصاد و حسابداری | بازاریابی و فروش | روان‌شناسی | امور اداری و منابع انسانی | رایانه و الکترونیک | زیست‌شناسی | آموزش و تدریس | ریاضیات | حقوق و مقررات دولتی | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | اداری | اقتصاد و حسابداری | فروش و بازاریابی | روان‌شناسی | پرسنل و منابع انسانی | رایانه و الکترونیک | زیست‌شناسی | آموزش و پرورش | ریاضیات | قانون و دولت | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | دید نزدیک | حساسیت به مسئله | تشخیص گفتار | مرتب‌سازی اطلاعات | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | استدلال استقرایی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | بینایی نزدیک | حساسیت به مسئله | تشخیص گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران عامل و مدیران ارشد اجرایی | مددکاران اجتماعی حوزه کودک، خانواده و مدارس | پزشکان و کارشناسان پزشکی قانونی | اپراتورهای تأسیسات سوزاندن اجساد (در صورت وجود) | مدیران مراکز پیش‌دبستانی و مهدکودک | کارشناسان مومیایی و آماده‌سازی اجساد | سرپرستان رده‌اول کارکنان خدمات فردی | متصدیان تشریفات و خدمات آرامستان | مدیران ارشد اجرایی و عملیاتی | کمک‌یاران خدمات مراقبت در منزل | نمایندگان فروش بیمه | مدیران خدمات درمانی و بهداشتی | برنامه‌ریزان همایش‌ها، تشریفات و رویدادها | کارگزاران و مجریان ترتیبات ترحیم و خاک‌سپاری | کارشناسان حقوق و امور بیماران | مراقبان خدمات فردی | مشاوران توان‌بخشی | سرپرستان خوابگاه‌ها و مراکز اقامتی | مدیران خدمات اجتماعی و خدمات مردمی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران عامل و مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | پزشکان قانونی و بازرسان مرگ مشکوک | اپراتورهای کوره‌های سوزاندن جسد | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | مومیایی‌کنندگان و فن‌ورزان کالبدآرایی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | متصدیان و دستیاران خدمات مراسم ترحیم | مدیران کل و مدیران عملیات | مراقبان سلامت و بهیاران مراقبت در منزل | نمایندگان و کارشناسان فروش بیمه | مدیران خدمات درمانی و بهداشتی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مدیران و برگزارکنندگان مراسم تشییع و تدفین | کارشناسان امور بیماران و پذیرش | مراقبان خدمات شخصی و همراهان توان‌خواهان | مشاوران توانبخشی | سرپرستان و مشاوران خوابگاه | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | امور اداری و منابع انسانی | بازاریابی و فروش | زبان انگلیسی | اقتصاد و حسابداری | آموزش و تدریس | روان‌شناسی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | پرسنل و منابع انسانی | فروش و بازاریابی | زبان انگلیسی | اقتصاد و حسابداری | آموزش و پرورش | روان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | تمرکز و توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تقسیم توجه | چابکی انگشتان | چابکی دستی | دید دور | به خاطرسپاری | روانی ایده‌ها | بیان کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>هماهنگ‌کنندگان خدمات تندرستی و آمادگی جسمانی | مدیران مراکز اسپا و ماساژ | مدیران آرامستان‌ها و امور متوفیات | مدیران هتل‌ها و مراکز اقامتی | مدیران خدمات پذیرایی و غذا | مدیران اماکن سرگرمی و بازی‌های مجاز | مدیران تفریحات و سرگرمی (به‌جز بازی‌های مجاز) | مدیران ارشد اجرایی و عملیاتی | مدیران خدمات اداری | مدیران املاک، مستغلات و مجتمع‌های مسکونی | مدیران خدمات اجتماعی و خدمات مردمی | مدیران منابع انسانی | مدیران فروش | مدیران بازاریابی | مدیران عامل و مدیران ارشد اجرایی | مدیران خدمات درمانی و بهداشتی | مدیران خرید و بازرگانی | مدیران آموزش و توسعه منابع انسانی | سرپرستان رده‌اول کارکنان خدمات فردی | کارکنان خدمات فردی و مراقبتی، سایر مشاغل</t>
+          <t>مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | مدیران مراکز خدمات اسپا و مراقبت‌های زیبایی | مدیران آرامستان‌ها و امور خدمات متوفیات | مدیران هتل و مراکز اقامتی | مدیران خدمات پذیرایی و غذا و نوشیدنی | مدیران سالن‌ها و بازی‌های تفریحی دارای مجوز | مدیران مجموعه‌های تفریحی، ورزشی و رویدادها | مدیران کل و مدیران عملیات | مدیران خدمات اداری و پشتیبانی | مدیران املاک، مستغلات و مجتمع‌های مسکونی | مدیران خدمات اجتماعی و خدمات مردمی | مدیران منابع انسانی | مدیران فروش | مدیران بازاریابی | مدیران عامل و مدیران ارشد اجرایی | مدیران خدمات درمانی و بهداشتی | مدیران خرید و تدارکات | مدیران آموزش و بهسازی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سایر کارکنان و ارائه‌دهندگان خدمات مراقبت فردی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
